--- a/data/raw/GLNPO 2024 Spring/Huron/D100/HU 15M D100 Spring 2024 24G400I73 Zoops.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Huron/D100/HU 15M D100 Spring 2024 24G400I73 Zoops.xlsx
@@ -5,16 +5,19 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\GLNPO 2024 Spring\Huron\D100\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Huron\D100\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EE04AA7-5087-44C4-8115-524ED6BF7FAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0432DF8E-92F1-4744-AD0C-7761A6E003F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1457C30C-13F4-4174-932E-EF619D2D1E63}"/>
+    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{1457C30C-13F4-4174-932E-EF619D2D1E63}"/>
   </bookViews>
   <sheets>
     <sheet name="HU 15M D100 Spring 2024 24G400I" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'HU 15M D100 Spring 2024 24G400I'!$A$1:$R$340</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
@@ -1128,12 +1131,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4FAFBBCE-377B-47C0-B176-E9AF1A8C33E6}">
   <dimension ref="A1:AA340"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="28.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1189,7 +1194,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -1248,7 +1253,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -1322,7 +1327,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -1387,7 +1392,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -1455,7 +1460,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -1520,7 +1525,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1585,7 +1590,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -1650,7 +1655,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -1715,7 +1720,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1780,7 +1785,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1848,7 +1853,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -1919,7 +1924,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1990,7 +1995,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -2058,7 +2063,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2126,7 +2131,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2194,7 +2199,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -2250,7 +2255,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -2321,7 +2326,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -2374,7 +2379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -2427,7 +2432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -2489,7 +2494,7 @@
         <v>1.0049999999999999</v>
       </c>
     </row>
-    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -2548,7 +2553,7 @@
         <v>0.996</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -2610,7 +2615,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -2669,7 +2674,7 @@
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -2728,7 +2733,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -2787,7 +2792,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -2843,7 +2848,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -2896,7 +2901,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -2949,7 +2954,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -3002,7 +3007,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -3055,7 +3060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -3108,7 +3113,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -3161,7 +3166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -3214,7 +3219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -3267,7 +3272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -3320,7 +3325,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -3373,7 +3378,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -3426,7 +3431,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -3479,7 +3484,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -3535,7 +3540,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -3588,7 +3593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -3641,7 +3646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -3694,7 +3699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -3747,7 +3752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -3800,7 +3805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -3853,7 +3858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -3906,7 +3911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -3959,7 +3964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -4012,7 +4017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -4065,7 +4070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -4118,7 +4123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -4171,7 +4176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -4224,7 +4229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -4277,7 +4282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -4333,7 +4338,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -4386,7 +4391,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -4439,7 +4444,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -4492,7 +4497,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -4545,7 +4550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -4598,7 +4603,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -4651,7 +4656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -4704,7 +4709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -4757,7 +4762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -4810,7 +4815,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -4863,7 +4868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -4916,7 +4921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -4969,7 +4974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -5022,7 +5027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -5075,7 +5080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -5128,7 +5133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -5181,7 +5186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -5234,7 +5239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -5287,7 +5292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -5340,7 +5345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -5393,7 +5398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -5446,7 +5451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -5499,7 +5504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -5552,7 +5557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -5605,7 +5610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -5658,7 +5663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -5711,7 +5716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -5764,7 +5769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -5817,7 +5822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -5870,7 +5875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -5923,7 +5928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -5976,7 +5981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -6029,7 +6034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -6082,7 +6087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -6135,7 +6140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -6188,7 +6193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -6241,7 +6246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -6294,7 +6299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -6347,7 +6352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -6400,7 +6405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -6453,7 +6458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -6509,7 +6514,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -6562,7 +6567,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -6615,7 +6620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -6668,7 +6673,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -6721,7 +6726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -6774,7 +6779,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -6830,7 +6835,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -6883,7 +6888,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -6939,7 +6944,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -6992,7 +6997,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -7045,7 +7050,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -7098,7 +7103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -7151,7 +7156,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -7204,7 +7209,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -7257,7 +7262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -7310,7 +7315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -7363,7 +7368,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -7416,7 +7421,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -7469,7 +7474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -7522,7 +7527,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -7575,7 +7580,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -7628,7 +7633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -7681,7 +7686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -7734,7 +7739,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -7787,7 +7792,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -7840,7 +7845,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -7893,7 +7898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -7946,7 +7951,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -7999,7 +8004,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -8052,7 +8057,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -8105,7 +8110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -8158,7 +8163,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -8211,7 +8216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -8264,7 +8269,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -8317,7 +8322,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -8370,7 +8375,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -8423,7 +8428,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -8476,7 +8481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -8529,7 +8534,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -8582,7 +8587,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -8635,7 +8640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -8688,7 +8693,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -8741,7 +8746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -8794,7 +8799,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -8847,7 +8852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -8900,7 +8905,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -8953,7 +8958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -9006,7 +9011,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -9059,7 +9064,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -9112,7 +9117,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -9165,7 +9170,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -9218,7 +9223,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -9271,7 +9276,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -9324,7 +9329,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -9377,7 +9382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -9430,7 +9435,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -9483,7 +9488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -9536,7 +9541,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -9589,7 +9594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -9642,7 +9647,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -9695,7 +9700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -9748,7 +9753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -9801,7 +9806,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -9854,7 +9859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -9907,7 +9912,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -9960,7 +9965,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -10013,7 +10018,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -10066,7 +10071,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -10119,7 +10124,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -10172,7 +10177,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -10225,7 +10230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -10278,7 +10283,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -10331,7 +10336,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -10384,7 +10389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -10437,7 +10442,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -10490,7 +10495,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -10543,7 +10548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -10596,7 +10601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -10649,7 +10654,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -10702,7 +10707,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -10755,7 +10760,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -10808,7 +10813,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -10861,7 +10866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -10914,7 +10919,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -10967,7 +10972,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -11020,7 +11025,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -11073,7 +11078,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -11126,7 +11131,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -11179,7 +11184,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -11232,7 +11237,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -11285,7 +11290,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -11338,7 +11343,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -11391,7 +11396,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -11444,7 +11449,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -11497,7 +11502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -11550,7 +11555,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -11603,7 +11608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -11656,7 +11661,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -11709,7 +11714,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -11762,7 +11767,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -11815,7 +11820,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -11868,7 +11873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -11921,7 +11926,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -11974,7 +11979,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -12027,7 +12032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -12080,7 +12085,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -12133,7 +12138,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -12186,7 +12191,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -12239,7 +12244,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -12292,7 +12297,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -12345,7 +12350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -12398,7 +12403,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -12451,7 +12456,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -12504,7 +12509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -12557,7 +12562,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -12610,7 +12615,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -12663,7 +12668,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -12716,7 +12721,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -12769,7 +12774,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -12822,7 +12827,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -12875,7 +12880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -12928,7 +12933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -12981,7 +12986,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="219" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -13034,7 +13039,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -13087,7 +13092,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -13140,7 +13145,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -13193,7 +13198,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -13246,7 +13251,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="224" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -13299,7 +13304,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -13352,7 +13357,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -13405,7 +13410,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -13458,7 +13463,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -13511,7 +13516,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -13564,7 +13569,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -13617,7 +13622,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -13670,7 +13675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -13726,7 +13731,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -13779,7 +13784,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -13832,7 +13837,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -13885,7 +13890,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -13938,7 +13943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -13991,7 +13996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -14044,7 +14049,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -14097,7 +14102,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -14150,7 +14155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -14203,7 +14208,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -14256,7 +14261,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -14309,7 +14314,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -14362,7 +14367,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -14415,7 +14420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -14468,7 +14473,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="247" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -14521,7 +14526,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="248" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -14574,7 +14579,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="249" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -14627,7 +14632,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="250" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -14680,7 +14685,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="251" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -14733,7 +14738,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="252" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -14786,7 +14791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="253" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -14839,7 +14844,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -14892,7 +14897,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>18</v>
       </c>
@@ -14945,7 +14950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>18</v>
       </c>
@@ -14998,7 +15003,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>18</v>
       </c>
@@ -15051,7 +15056,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>18</v>
       </c>
@@ -15104,7 +15109,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="259" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>18</v>
       </c>
@@ -15157,7 +15162,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="260" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -15210,7 +15215,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="261" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>18</v>
       </c>
@@ -15263,7 +15268,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="262" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>18</v>
       </c>
@@ -15316,7 +15321,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="263" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>18</v>
       </c>
@@ -15369,7 +15374,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="264" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>18</v>
       </c>
@@ -15422,7 +15427,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="265" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>18</v>
       </c>
@@ -15475,7 +15480,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="266" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A266" t="s">
         <v>18</v>
       </c>
@@ -15528,7 +15533,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="267" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>18</v>
       </c>
@@ -15581,7 +15586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -15634,7 +15639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>18</v>
       </c>
@@ -15687,7 +15692,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="270" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>18</v>
       </c>
@@ -15740,7 +15745,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="271" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -15793,7 +15798,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="272" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>18</v>
       </c>
@@ -15846,7 +15851,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="273" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>18</v>
       </c>
@@ -15899,7 +15904,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="274" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -15952,7 +15957,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="275" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -16005,7 +16010,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="276" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A276" t="s">
         <v>18</v>
       </c>
@@ -16058,7 +16063,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="277" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -16111,7 +16116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -16164,7 +16169,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="279" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -16217,7 +16222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -16270,7 +16275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -16323,7 +16328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -16376,7 +16381,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="283" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -16429,7 +16434,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="284" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -16482,7 +16487,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="285" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A285" t="s">
         <v>18</v>
       </c>
@@ -16535,7 +16540,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="286" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -16588,7 +16593,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="287" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -16641,7 +16646,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="288" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -16694,7 +16699,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="289" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A289" t="s">
         <v>18</v>
       </c>
@@ -16747,7 +16752,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="290" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -16800,7 +16805,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="291" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -16853,7 +16858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="292" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -16906,7 +16911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="293" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -16959,7 +16964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -17012,7 +17017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -17065,7 +17070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -17118,7 +17123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -17171,7 +17176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -17224,7 +17229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -17277,7 +17282,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="300" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -17330,7 +17335,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="301" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -17383,7 +17388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="302" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A302" t="s">
         <v>18</v>
       </c>
@@ -17436,7 +17441,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="303" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>18</v>
       </c>
@@ -17489,7 +17494,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="304" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A304" t="s">
         <v>18</v>
       </c>
@@ -17542,7 +17547,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>18</v>
       </c>
@@ -17595,7 +17600,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>18</v>
       </c>
@@ -17648,7 +17653,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -17701,7 +17706,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -17754,7 +17759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>18</v>
       </c>
@@ -17810,7 +17815,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>18</v>
       </c>
@@ -17863,7 +17868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>18</v>
       </c>
@@ -17916,7 +17921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>18</v>
       </c>
@@ -17969,7 +17974,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>18</v>
       </c>
@@ -18022,7 +18027,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -18075,7 +18080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A315" t="s">
         <v>18</v>
       </c>
@@ -18128,7 +18133,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>18</v>
       </c>
@@ -18181,7 +18186,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>18</v>
       </c>
@@ -18234,7 +18239,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -18287,7 +18292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>18</v>
       </c>
@@ -18340,7 +18345,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>18</v>
       </c>
@@ -18393,7 +18398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>18</v>
       </c>
@@ -18446,7 +18451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>18</v>
       </c>
@@ -18499,7 +18504,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>18</v>
       </c>
@@ -18552,7 +18557,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>18</v>
       </c>
@@ -18605,7 +18610,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>18</v>
       </c>
@@ -18658,7 +18663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>18</v>
       </c>
@@ -18711,7 +18716,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>18</v>
       </c>
@@ -18764,7 +18769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>18</v>
       </c>
@@ -18817,7 +18822,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>18</v>
       </c>
@@ -18870,7 +18875,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>18</v>
       </c>
@@ -18923,7 +18928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>18</v>
       </c>
@@ -18976,7 +18981,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>18</v>
       </c>
@@ -19032,7 +19037,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>18</v>
       </c>
@@ -19085,7 +19090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>18</v>
       </c>
@@ -19138,7 +19143,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>18</v>
       </c>
@@ -19170,16 +19175,16 @@
         <v>24</v>
       </c>
       <c r="K335" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L335" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="M335" t="s">
-        <v>53</v>
+        <v>27</v>
       </c>
       <c r="N335" t="s">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="O335" t="s">
         <v>55</v>
@@ -19191,7 +19196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>18</v>
       </c>
@@ -19244,7 +19249,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>18</v>
       </c>
@@ -19297,7 +19302,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>18</v>
       </c>
@@ -19350,7 +19355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>18</v>
       </c>
@@ -19403,7 +19408,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A340" t="s">
         <v>18</v>
       </c>
@@ -19457,6 +19462,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R340" xr:uid="{4FAFBBCE-377B-47C0-B176-E9AF1A8C33E6}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>